--- a/Employee_Reports_wi48/Chalana Ishan Dishanayake Dishanayake Pathiranage Q0569.xlsx
+++ b/Employee_Reports_wi48/Chalana Ishan Dishanayake Dishanayake Pathiranage Q0569.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-328</v>
+        <v>-331</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-328</v>
+        <v>-331</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1595,9 +1595,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1609,11 +1621,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1658,11 +1670,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1707,11 +1719,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1756,11 +1768,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1793,11 +1805,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1830,11 +1842,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1867,11 +1879,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1916,11 +1928,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1965,11 +1977,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2002,11 +2014,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2051,11 +2063,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2088,11 +2100,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
